--- a/app/development/catalogo/data/catalogo_responsabilidades.xlsx
+++ b/app/development/catalogo/data/catalogo_responsabilidades.xlsx
@@ -94,6 +94,15 @@
     <t xml:space="preserve">PROCESSO PA</t>
   </si>
   <si>
+    <t xml:space="preserve">PS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROCESSO SUBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROCESSO </t>
+  </si>
+  <si>
     <t xml:space="preserve">AC </t>
   </si>
   <si>
@@ -161,15 +170,6 @@
   </si>
   <si>
     <t xml:space="preserve">RETORNO DE VENDAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROCESSO SUBS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROCESSO </t>
   </si>
 </sst>
 </file>
@@ -271,7 +271,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.69"/>
@@ -444,131 +444,137 @@
         <v>28</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>26</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="E16" s="1"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>49</v>
-      </c>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0"/>
+      <c r="B26" s="0"/>
+      <c r="C26" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
